--- a/data/raw/ofertas_consolidadas.xlsx
+++ b/data/raw/ofertas_consolidadas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L184"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11519,6 +11519,6734 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>4434428862</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>PRGX Global Inc.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Sr Data Scientist en PRGX Global Inc. (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/sr-data-scientist-at-prgx-global-inc-4434428862</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>4471110914</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>hiberus</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Scientist en hiberus (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-scientist-at-hiberus-4471110914</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>4469576118</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Científico de Datos</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Crezcamos S.A.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Bucaramanga, Santander, Colombia</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Científico de Datos en Crezcamos S.A. (Bucaramanga, Santander, Colombia).</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/cient%C3%ADfico-de-datos-at-crezcamos-s-a-4469576118</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>4464166071</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Científico de Datos II</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Centro de Empleo y Talento</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Científico de Datos II en Centro de Empleo y Talento (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/cient%C3%ADfico-de-datos-ii%C2%A0-at-centro-de-empleo-y-talento-4464166071</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>4469938256</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Científico/a de Datos Databricks</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Porvenir Pensiones y Cesantías</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Científico/a de Datos Databricks en Porvenir Pensiones y Cesantías (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/cient%C3%ADfico-a-de-datos-databricks-at-porvenir-pensiones-y-cesant%C3%ADas-4469938256</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>4469464951</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Analyst I, Data Science</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Liberty Specialty Markets Latam</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analyst I, Data Science en Liberty Specialty Markets Latam (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analyst-i-data-science-at-liberty-specialty-markets-latam-4469464951</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>4469487008</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Analyst II, Data Science</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Liberty Specialty Markets Latam</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analyst II, Data Science en Liberty Specialty Markets Latam (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analyst-ii-data-science-at-liberty-specialty-markets-latam-4469487008</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>4478466269</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Data Scientist – Optimization &amp; Geospatial</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>NTT DATA, Inc.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Scientist – Optimization &amp; Geospatial en NTT DATA, Inc. (Colombia).</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-scientist-%E2%80%93-optimization-geospatial-at-ntt-data-inc-4478466269</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>4458347689</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Data Analyst-Business Intelligence</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Analyst-Business Intelligence en IQVIA (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-analyst-business-intelligence-at-iqvia-4458347689</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>4468663693</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Ingeniero de datos - Senior</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Nubika Digital - Inetum Group</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero de datos - Senior en Nubika Digital - Inetum Group (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-de-datos-senior-at-nubika-cloud-solutions-4468663693</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>4479603376</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Data Analyst | Business Intelligence</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Analyst | Business Intelligence en IQVIA (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-analyst-business-intelligence-at-iqvia-4479603376</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>4480139686</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Consultor(a) Jr. Artificial Intelligence and Data - Medellín</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Área metropolitana de Medellín</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Consultor(a) Jr. Artificial Intelligence and Data - Medellín en Deloitte (Área metropolitana de Medellín).</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/consultor-a-jr-artificial-intelligence-and-data-medell%C3%ADn-at-deloitte-4480139686</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4258067001</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Remote Work | REF#256309</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Montería, Córdoba, Colombia</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Analyst - Remote Work | REF#256309 en BairesDev (Montería, Córdoba, Colombia).</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-analyst-remote-work-ref%23256309-at-bairesdev-4258067001</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>4466925031</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Analista de datos</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Hitss Colombia</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analista de datos en Hitss Colombia (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-datos-at-hitss-colombia-4466925031</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>4474353207</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Senior Power BI Data Analyst - Remote Work | REF#300673</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Power BI Data Analyst - Remote Work | REF#300673 en BairesDev (Colombia).</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-power-bi-data-analyst-remote-work-ref%23300673-at-bairesdev-4474353207</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>4480537356</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Analista de Datos y BI</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Innova Schools Colombia</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analista de Datos y BI en Innova Schools Colombia (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-datos-y-bi-at-innova-schools-colombia-4480537356</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>4471156305</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Analista de Inteligencia de Negocios</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Interaseo S.A.S. E.S.P.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analista de Inteligencia de Negocios en Interaseo S.A.S. E.S.P. (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-inteligencia-de-negocios-at-interaseo-s-a-s-e-s-p-4471156305</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>4470500792</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Analista de Datos - Mercado Envíos</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analista de Datos - Mercado Envíos en Mercado Libre (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-datos-mercado-env%C3%ADos-at-mercado-libre-4470500792</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>4475819796</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Falabella</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Analyst en Falabella (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-analyst-at-falabella-4475819796</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>4462823043</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Analista de datos SQL/AWS</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Inter Rapidísimo</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analista de datos SQL/AWS en Inter Rapidísimo (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-datos-sql-aws-at-inter-rapid%C3%ADsimo-4462823043</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>4472393150</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ANALISTA DE DATOS / BI AZURE</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>PERCEPTIO S.A.S.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para ANALISTA DE DATOS / BI AZURE en PERCEPTIO S.A.S. (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-datos-bi-azure-at-perceptio-s-a-s-4472393150</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4468898336</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Sr. BI Analyst</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Edgewell Personal Care</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Sr. BI Analyst en Edgewell Personal Care (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/sr-bi-analyst-at-edgewell-personal-care-4468898336</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>4469193842</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Auxis</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Analyst en Auxis (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-analyst-at-auxis-4469193842</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>4479236020</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>HR DATA &amp; INSIGHTS ANALYST</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Svitla Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para HR DATA &amp; INSIGHTS ANALYST en Svitla Systems, Inc. (Colombia).</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/hr-data-insights-analyst-at-svitla-systems-inc-4479236020</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>4473586630</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>TP-Link Colombia</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Área metropolitana de Bogotá D.C.</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Business Intelligence Analyst en TP-Link Colombia (Área metropolitana de Bogotá D.C.).</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/business-intelligence-analyst-at-tp-link-colombia-4473586630</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>4458548569</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Data Intelligence Specialist</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>GEODIS</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Intelligence Specialist en GEODIS (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-intelligence-specialist-at-geodis-4458548569</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>4474597249</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Especialista de Data &amp; Metrics</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Marsh</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Especialista de Data &amp; Metrics en Marsh (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/especialista-de-data-metrics-at-marsh-4474597249</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>4475081660</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Procurement Analytics Professional / Finance / Data Analyst / Procurement / Remote / Bilingual</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Iron Mountain</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Procurement Analytics Professional / Finance / Data Analyst / Procurement / Remote / Bilingual en Iron Mountain (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/procurement-analytics-professional-finance-data-analyst-procurement-remote-bilingual-at-iron-mountain-4475081660</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>4475091196</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Procurement Analytics Professional / Finance / Data Analyst / Procurement / Remote / Bilingual</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Iron Mountain</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Sabaneta, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Procurement Analytics Professional / Finance / Data Analyst / Procurement / Remote / Bilingual en Iron Mountain (Sabaneta, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/procurement-analytics-professional-finance-data-analyst-procurement-remote-bilingual-at-iron-mountain-4475091196</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>4480190198</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Analista Data Quality</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Biako Seguridad</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analista Data Quality en Biako Seguridad (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-data-quality-at-biako-seguridad-4480190198</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>4473275852</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Data Services Reports &amp; Insights Analyst</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Cloudbeds</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Services Reports &amp; Insights Analyst en Cloudbeds (Colombia).</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-services-reports-insights-analyst-at-cloudbeds-4473275852</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>4191843703</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Business Data Analyst</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Performics</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Business Data Analyst en Performics (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/business-data-analyst-at-performics-4191843703</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>4478771492</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Data Marketing Analyst - Remote</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>KNN Digital Media</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Marketing Analyst - Remote en KNN Digital Media (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-marketing-analyst-remote-at-knn-digital-media-4478771492</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>4474365667</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ANALISTA DE DATOS MAESTROS COMERCIALES</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Holcim ABS</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para ANALISTA DE DATOS MAESTROS COMERCIALES en Holcim ABS (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-datos-maestros-comerciales-at-holcim-abs-4474365667</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>4479893399</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Regional Claims BI Analyst</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Chubb</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Regional Claims BI Analyst en Chubb (Colombia).</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/regional-claims-bi-analyst-at-chubb-4479893399</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4469985271</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Performance Data Analyst</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Amrize</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Performance Data Analyst en Amrize (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/performance-data-analyst-at-amrize-4469985271</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>4474774014</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Analista de datos</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Omnicom Media Colombia</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Analista de datos en Omnicom Media Colombia (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/analista-de-datos-at-omnicom-media-colombia-4474774014</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>4479881448</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Consultor en Analítica de Datos y Reportabilidad</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Worley</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Consultor en Analítica de Datos y Reportabilidad en Worley (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/consultor-en-anal%C3%ADtica-de-datos-y-reportabilidad-at-worley-4479881448</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>4477312991</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Growth Data Analyst</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Rappi</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Growth Data Analyst en Rappi (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/growth-data-analyst-at-rappi-4477312991</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>4470672333</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Especialista Senior en Data &amp; Analytics (Foco en Negocio)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>CGI</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Especialista Senior en Data &amp; Analytics (Foco en Negocio) en CGI (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/especialista-senior-en-data-analytics-foco-en-negocio-at-cgi-4470672333</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>4478138336</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>EXL</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Analyst en EXL (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-analyst-at-exl-4478138336</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>4461919360</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Lead Data Analyst</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Lead Data Analyst en EPAM Systems (Colombia).</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/lead-data-analyst-at-epam-systems-4461919360</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>4467774892</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Data Engineer AWS/PySpark</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>myCloudDoor</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer AWS/PySpark en myCloudDoor (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-aws-pyspark-at-myclouddoor-4467774892</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>4479228094</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer - Remote Work | REF#302142</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Azure Data Engineer - Remote Work | REF#302142 en BairesDev (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/azure-data-engineer-remote-work-ref%23302142-at-bairesdev-4479228094</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>4258062363</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ETL + Data Engineer - REMOTE WORK | REF#241733</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Pereira, Risaralda, Colombia</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para ETL + Data Engineer - REMOTE WORK | REF#241733 en BairesDev (Pereira, Risaralda, Colombia).</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/etl-%2B-data-engineer-remote-work-ref%23241733-at-bairesdev-4258062363</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>4468187901</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Antenna</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer en Antenna (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-at-antenna-4468187901</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>4469869145</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Loka</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer en Loka (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-at-loka-4469869145</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>4477633461</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Data Engineer (Databricks)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Wizeline</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (Databricks) en Wizeline (Colombia).</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-databricks-at-wizeline-4477633461</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>4471568695</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Ingeniero/a de Datos - Kafka</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>NTT DATA Europe &amp; Latam</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero/a de Datos - Kafka en NTT DATA Europe &amp; Latam (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-a-de-datos-kafka-at-ntt-data-europe-latam-4471568695</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>4472091944</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Ingeniero de datos</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Credicorp Capital</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero de datos en Credicorp Capital (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-de-datos-at-credicorp-capital-4472091944</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>4475029944</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Ingeniería de Datos Azure - Databricks</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>GFT Technologies LATAM</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniería de Datos Azure - Databricks en GFT Technologies LATAM (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingenier%C3%ADa-de-datos-azure-databricks-at-gft-technologies-latam-4475029944</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>4215906903</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Programador Senior - Data Engineering</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Inetum</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Programador Senior - Data Engineering en Inetum (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/programador-senior-data-engineering-at-inetum-4215906903</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>4479541079</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Bia Energy</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en Bia Energy (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-bia-energy-4479541079</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>4475049014</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Ingeniero/a de Datos | SQL · ETL · Data Quality · Power BI</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Minsait</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero/a de Datos | SQL · ETL · Data Quality · Power BI en Minsait (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-a-de-datos-sql-%C2%B7-etl-%C2%B7-data-quality-%C2%B7-power-bi-at-minsait-4475049014</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>4479850204</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Lean Solutions Group</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en Lean Solutions Group (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-lean-solutions-group-4479850204</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>4410955202</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Data Engineer | Latam</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Cuesta Partners</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer | Latam en Cuesta Partners (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-latam-at-cuesta-partners-4410955202</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>4471131067</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – AWS / Databricks</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>hiberus</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer – AWS / Databricks en hiberus (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-%E2%80%93-aws-databricks-at-hiberus-4471131067</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>4478138653</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (SQL, dbt)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Exadel</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (SQL, dbt) en Exadel (Colombia).</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-sql-dbt-at-exadel-4478138653</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>4475738197</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer en EPAM Systems (Colombia).</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-at-epam-systems-4475738197</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>4470185279</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Deel</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer en Deel (Colombia).</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-at-deel-4470185279</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>4476503516</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en Gallagher (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-gallagher-4476503516</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>4471151018</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos GCP + IA Generativa</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Bluetab, an IBM Company (América)</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero de Datos GCP + IA Generativa en Bluetab, an IBM Company (América) (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-de-datos-gcp-%2B-ia-generativa-at-bluetab-an-ibm-company-am%C3%A9rica-4471151018</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>4439977940</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>8020REI</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer en 8020REI (Colombia).</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-at-8020rei-4439977940</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>4466201578</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Data Engineer Expert</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Softtek</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer Expert en Softtek (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-expert-at-softtek-4466201578</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>4478561205</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Earnix)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Encora Inc.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (Earnix) en Encora Inc. (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-earnix-at-encora-inc-4478561205</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>4461915640</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Integration Engineer en EPAM Systems (Colombia).</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-integration-engineer-at-epam-systems-4461915640</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>4474985973</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Ingeniero Datos</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Global MVM</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero Datos en Global MVM (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-datos-at-global-mvm-4474985973</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>4449903110</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - (Talent Pool / Future Opportunities)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer - (Talent Pool / Future Opportunities) en Monks (Colombia).</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-talent-pool-future-opportunities-at-monks-4449903110</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>4479551324</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Parser</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (Databricks) en Parser (Colombia).</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-databricks-at-parser-4479551324</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>4436116509</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Data Engineer Semi Senior</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>VASS</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer Semi Senior en VASS (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-semi-senior-at-vass-4436116509</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>4471742564</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Senior Data Engineering</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Publicis Sapient</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineering en Publicis Sapient (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineering-at-publicis-sapient-4471742564</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>4415705281</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Perform</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en Perform (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-perform-4415705281</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>4474363749</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Power BI</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Perficient</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer - Power BI en Perficient (Colombia).</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-power-bi-at-perficient-4474363749</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>4471205879</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Lean Tech, a Lean Solutions Group Division</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Medellin, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer en Lean Tech, a Lean Solutions Group Division (Medellin, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-at-lean-tech-a-lean-solutions-group-division-4471205879</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>4469965967</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (GCP &amp; Data Integration)</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Applaudo</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (GCP &amp; Data Integration) en Applaudo (Colombia).</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-gcp-data-integration-at-applaudo-4469965967</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>4459430896</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Staff Data Engineer</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Staff Data Engineer en Robots &amp; Pencils (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/staff-data-engineer-at-robots-pencils-4459430896</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>4462431955</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>RedCloud Consulting</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en RedCloud Consulting (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-redcloud-consulting-4462431955</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>4471813362</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Grupo QBCo</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero de Datos en Grupo QBCo (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-de-datos-at-grupo-qbco-4471813362</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>4467886830</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer &amp; Architect (Snowflake &amp; GCP)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>N-iX</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Lead Data Engineer &amp; Architect (Snowflake &amp; GCP) en N-iX (Colombia).</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/lead-data-engineer-architect-snowflake-gcp-at-n-ix-4467886830</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>4472803995</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Data Engineer - Colombia</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Slalom</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer - Colombia en Slalom (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-colombia-at-slalom-4472803995</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>4479170411</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Data Engineer, AI &amp; Cloud</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Keyrus</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer, AI &amp; Cloud en Keyrus (Colombia).</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-ai-cloud-at-keyrus-4479170411</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>4464906561</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks) - Remote Work | REF#303334</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (Databricks) - Remote Work | REF#303334 en BairesDev (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-databricks-remote-work-ref%23303334-at-bairesdev-4464906561</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>4464698677</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Azure) - Remote Work | REF#303645</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (Azure) - Remote Work | REF#303645 en BairesDev (Colombia).</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-azure-remote-work-ref%23303645-at-bairesdev-4464698677</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>4464900715</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer 2 - Remote Work | REF#297228</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer 2 - Remote Work | REF#297228 en BairesDev (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-2-remote-work-ref%23297228-at-bairesdev-4464900715</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>4474348697</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks) - Remote Work | REF#304690</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (Databricks) - Remote Work | REF#304690 en BairesDev (Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-databricks-remote-work-ref%23304690-at-bairesdev-4474348697</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>4459056627</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Data Engineer (AWS) - Remote Work | REF#302136</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (AWS) - Remote Work | REF#302136 en BairesDev (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-aws-remote-work-ref%23302136-at-bairesdev-4459056627</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>4464692728</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Data Engineer (SAP + Snowflake) - Remote Work | REF#303329</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>CAUCA, Sucre, Colombia</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (SAP + Snowflake) - Remote Work | REF#303329 en BairesDev (CAUCA, Sucre, Colombia).</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-sap-%2B-snowflake-remote-work-ref%23303329-at-bairesdev-4464692728</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>4474344795</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer (Apache Spark) - Remote work | REF#305093</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Databricks Data Engineer (Apache Spark) - Remote work | REF#305093 en BairesDev (Colombia).</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/databricks-data-engineer-apache-spark-remote-work-ref%23305093-at-bairesdev-4474344795</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>4449093322</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Data Engineer (Databricks) - Remote Work | REF#299534</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (Databricks) - Remote Work | REF#299534 en BairesDev (Colombia).</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-databricks-remote-work-ref%23299534-at-bairesdev-4449093322</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>4462092040</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer 2 - Remote Work | REF#302636</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer 2 - Remote Work | REF#302636 en BairesDev (Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-2-remote-work-ref%23302636-at-bairesdev-4462092040</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>4474338913</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>AWS Data Engineer - Remote Work | REF#304823</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para AWS Data Engineer - Remote Work | REF#304823 en BairesDev (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/aws-data-engineer-remote-work-ref%23304823-at-bairesdev-4474338913</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>4479211947</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer (Apache Spark) - Remote work | REF#305826</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Databricks Data Engineer (Apache Spark) - Remote work | REF#305826 en BairesDev (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/databricks-data-engineer-apache-spark-remote-work-ref%23305826-at-bairesdev-4479211947</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>4480127140</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Data Engineer Senior</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Blend</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer Senior en Blend (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-senior-at-blend-4480127140</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>4440559743</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Blend</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Lead Data Engineer en Blend (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/lead-data-engineer-at-blend-4440559743</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>4469741237</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Ingeniero Senior de Datos – Data Lakehouse (PCD)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>COLOMBIANA DE VIGILANCIA Y SEGURIDAD - COLVISEG LTDA</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero Senior de Datos – Data Lakehouse (PCD) en COLOMBIANA DE VIGILANCIA Y SEGURIDAD - COLVISEG LTDA (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-senior-de-datos-%E2%80%93-data-lakehouse-pcd-at-colombiana-de-vigilancia-y-seguridad-colviseg-ltda-4469741237</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>4474604610</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos Senior</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>EXL</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero de Datos Senior en EXL (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-de-datos-senior-at-exl-4474604610</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>4478180917</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Ingeniero/a de datos senior</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Nequi</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero/a de datos senior en Nequi (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-a-de-datos-senior-at-nequi-4478180917</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>4460061065</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer (Azure)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>SoftServe</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Lead Data Engineer (Azure) en SoftServe (Colombia).</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/lead-data-engineer-azure-at-softserve-4460061065</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>4477090460</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Ingeniero de datos</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Fibrazo</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Medellín, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero de datos en Fibrazo (Medellín, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-de-datos-at-fibrazo-4477090460</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>4444002212</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Ingenieros de datos</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Accenture Colombia</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Medellin, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingenieros de datos en Accenture Colombia (Medellin, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingenieros-de-datos-at-accenture-colombia-4444002212</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>4460982830</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Zimmer Biomet</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en Zimmer Biomet (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-zimmer-biomet-4460982830</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>4432870029</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Data Engineer Associate, IB Analytics</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer Associate, IB Analytics en Scotiabank (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-associate-ib-analytics-at-scotiabank-4432870029</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>4468827682</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en Rockwell Automation (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-rockwell-automation-4468827682</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>4466212874</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Data Management and BI Manager, GOC</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>WPP Media</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Medellin, Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Management and BI Manager, GOC en WPP Media (Medellin, Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-management-and-bi-manager-goc-at-wpp-media-4466212874</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>4472371972</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DATA ENGINEER – MICROSOFT AZURE</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>PERCEPTIO S.A.S.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para DATA ENGINEER – MICROSOFT AZURE en PERCEPTIO S.A.S. (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-%E2%80%93-microsoft-azure-at-perceptio-s-a-s-4472371972</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>4479589994</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Lean Tech, a Lean Solutions Group Division</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer en Lean Tech, a Lean Solutions Group Division (Colombia).</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-at-lean-tech-a-lean-solutions-group-division-4479589994</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>4474623171</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Snowflake Data engineer</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>EXL</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Bogotá, Distrito Capital, Colombia</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Snowflake Data engineer en EXL (Bogotá, Distrito Capital, Colombia).</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/snowflake-data-engineer-at-exl-4474623171</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>4474995033</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>evolv Consulting</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer en evolv Consulting (Colombia).</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-at-evolv-consulting-4474995033</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>4479215989</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Crezcamos S.A.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Bucaramanga, Santander, Colombia</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Ingeniero de Datos en Crezcamos S.A. (Bucaramanga, Santander, Colombia).</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/ingeniero-de-datos-at-crezcamos-s-a-4479215989</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>4464905528</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Data Engineer (SAP + Snowflake) - Remote Work | REF#303323</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (SAP + Snowflake) - Remote Work | REF#303323 en BairesDev (Colombia).</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-sap-%2B-snowflake-remote-work-ref%23303323-at-bairesdev-4464905528</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>4464695719</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Data Engineer (Azure Databricks) - Remote Work | REF#295770</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>CAUCA, Sucre, Colombia</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (Azure Databricks) - Remote Work | REF#295770 en BairesDev (CAUCA, Sucre, Colombia).</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-azure-databricks-remote-work-ref%23295770-at-bairesdev-4464695719</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>4449079791</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Data Engineer (Azure) - Remote Work | REF#299837</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (Azure) - Remote Work | REF#299837 en BairesDev (Colombia).</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-azure-remote-work-ref%23299837-at-bairesdev-4449079791</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>4474342834</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Databricks) - Remote Work | REF#304691</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer (Databricks) - Remote Work | REF#304691 en BairesDev (Colombia).</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-databricks-remote-work-ref%23304691-at-bairesdev-4474342834</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>4474340880</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Data Engineer (Databricks) - Remote Work | REF#304688</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Antioquia, Colombia</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Data Engineer (Databricks) - Remote Work | REF#304688 en BairesDev (Antioquia, Colombia).</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/data-engineer-databricks-remote-work-ref%23304688-at-bairesdev-4474340880</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>4474347774</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer (Apache Spark) - Remote work | REF#305096</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>CAUCA, Sucre, Colombia</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Databricks Data Engineer (Apache Spark) - Remote work | REF#305096 en BairesDev (CAUCA, Sucre, Colombia).</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/databricks-data-engineer-apache-spark-remote-work-ref%23305096-at-bairesdev-4474347774</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>cientifico-de-datos</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>4474337926</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer 2 - Remote Work | REF#304701</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>CAUCA, Sucre, Colombia</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>A convenir / No especificado</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Oferta publicada en LinkedIn para Senior Data Engineer 2 - Remote Work | REF#304701 en BairesDev (CAUCA, Sucre, Colombia).</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>https://co.linkedin.com/jobs/view/senior-data-engineer-2-remote-work-ref%23304701-at-bairesdev-4474337926</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
